--- a/ValueSet-ng-hiv-local-concepts.xlsx
+++ b/ValueSet-ng-hiv-local-concepts.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="134">
   <si>
     <t>Property</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Nigeria HIV Local Concepts</t>
+    <t>NG HIV Local Concepts</t>
   </si>
   <si>
     <t>Status</t>
@@ -89,13 +89,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NDHI (https://digitalhealth.gov.ng, emeka2015@gmail.com)</t>
-  </si>
-  <si>
-    <t>Nigeria Digital in Health Initiative. (lekeojewale@gmail.com(Work))</t>
-  </si>
-  <si>
-    <t>Nigeria Digital in Health Initiative. (emeka2015@gmail.com(Work))</t>
+    <t>NDHI (https://digitalhealth.gov.ng)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -565,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -662,54 +656,38 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>25</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B15" t="s" s="2">
         <v>27</v>
       </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
+      <c r="B16" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -728,34 +706,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -774,82 +752,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -868,90 +846,90 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -970,34 +948,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1016,82 +994,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1110,34 +1088,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1156,10 +1134,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
@@ -1167,31 +1145,31 @@
         <v>15</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1210,66 +1188,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1288,74 +1266,74 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1374,58 +1352,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1444,90 +1422,90 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1546,82 +1524,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
